--- a/data/trans_bre/IP41-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP41-Clase-trans_bre.xlsx
@@ -660,17 +660,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 2,31</t>
+          <t>-10,7; 2,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 4,34</t>
+          <t>-7,73; 4,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 5,59</t>
+          <t>-11,1; 5,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -680,17 +680,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 2,51</t>
+          <t>-11,13; 2,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 4,77</t>
+          <t>-8,07; 4,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 6,52</t>
+          <t>-12,1; 6,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 3,84</t>
+          <t>-7,59; 3,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 7,46</t>
+          <t>-6,63; 8,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 1,93</t>
+          <t>-13,82; 1,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -780,17 +780,17 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 4,13</t>
+          <t>-7,92; 3,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 8,67</t>
+          <t>-7,32; 9,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,94; 2,35</t>
+          <t>-15,21; 1,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,17 +860,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 10,81</t>
+          <t>-1,21; 10,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 6,1</t>
+          <t>-5,86; 6,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 7,36</t>
+          <t>-7,14; 7,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -880,17 +880,17 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 12,51</t>
+          <t>-1,25; 12,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 6,79</t>
+          <t>-6,12; 7,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 8,32</t>
+          <t>-7,4; 8,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,17 +960,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 5,31</t>
+          <t>-4,39; 5,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 7,36</t>
+          <t>-2,93; 7,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 4,67</t>
+          <t>-7,28; 4,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 6,04</t>
+          <t>-4,74; 5,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 8,73</t>
+          <t>-3,29; 9,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 5,84</t>
+          <t>-8,38; 5,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,15; -0,01</t>
+          <t>-12,36; 0,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 6,64</t>
+          <t>-7,51; 6,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 9,03</t>
+          <t>-6,57; 8,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1080,17 +1080,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,78; -0,04</t>
+          <t>-12,86; 0,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 8,35</t>
+          <t>-8,59; 7,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 11,5</t>
+          <t>-7,76; 11,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 8,88</t>
+          <t>-7,77; 8,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 13,36</t>
+          <t>-6,2; 13,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,63; 26,11</t>
+          <t>2,03; 26,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 10,55</t>
+          <t>-8,27; 9,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 16,67</t>
+          <t>-6,98; 17,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,38; 42,24</t>
+          <t>2,69; 45,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1260,17 +1260,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 1,43</t>
+          <t>-3,61; 1,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 3,38</t>
+          <t>-1,8; 3,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 3,05</t>
+          <t>-3,42; 2,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1280,17 +1280,17 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 1,58</t>
+          <t>-3,88; 1,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 3,9</t>
+          <t>-2,02; 4,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 3,64</t>
+          <t>-3,98; 3,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">

--- a/data/trans_bre/IP41-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP41-Clase-trans_bre.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,8 +515,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,15 +531,13 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Brecha de género relativa</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -563,27 +559,17 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -596,8 +582,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -627,27 +611,17 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-4,2%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-4,2%</t>
+          <t>-1,21%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,21%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
           <t>-3,2%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -660,42 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 2,67</t>
+          <t>-10,41; 2,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 4,15</t>
+          <t>-7,44; 5,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 5,39</t>
+          <t>-11,99; 5,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-10,93; 2,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 2,95</t>
+          <t>-7,68; 5,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 4,42</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-12,1; 6,41</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-12,83; 6,27</t>
         </is>
       </c>
     </row>
@@ -727,27 +691,17 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-2,36%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-2,36%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
           <t>-6,51%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -760,42 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 3,58</t>
+          <t>-8,42; 3,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 8,39</t>
+          <t>-6,56; 7,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,82; 1,61</t>
+          <t>-13,28; 2,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,77; 3,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 3,72</t>
+          <t>-7,19; 8,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 9,99</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-15,21; 1,88</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-14,66; 3,04</t>
         </is>
       </c>
     </row>
@@ -827,27 +771,17 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
           <t>0,16%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -860,42 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 10,65</t>
+          <t>-1,62; 11,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 6,89</t>
+          <t>-5,7; 5,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 7,7</t>
+          <t>-7,71; 7,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,66; 13,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 12,06</t>
+          <t>-5,95; 6,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 7,68</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-7,4; 8,86</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-8,07; 8,1</t>
         </is>
       </c>
     </row>
@@ -927,27 +851,17 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
           <t>-1,46%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -960,42 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 5,15</t>
+          <t>-3,7; 5,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 7,53</t>
+          <t>-3,39; 7,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 4,78</t>
+          <t>-7,4; 4,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,06; 6,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 5,92</t>
+          <t>-3,78; 8,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 9,03</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-8,38; 5,9</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-8,52; 5,66</t>
         </is>
       </c>
     </row>
@@ -1027,27 +931,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-6,01%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-6,01%</t>
+          <t>-0,67%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,67%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
           <t>1,63%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,36; 0,36</t>
+          <t>-12,03; -0,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 6,19</t>
+          <t>-8,37; 5,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 8,83</t>
+          <t>-6,27; 10,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-12,59; -0,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 0,33</t>
+          <t>-9,57; 7,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 7,81</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-7,76; 11,51</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-7,32; 12,95</t>
         </is>
       </c>
     </row>
@@ -1127,27 +1011,17 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
           <t>21,65%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 8,37</t>
+          <t>-7,5; 8,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 13,52</t>
+          <t>-6,03; 14,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,03; 26,89</t>
+          <t>3,7; 26,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,16; 9,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 9,78</t>
+          <t>-6,63; 17,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 17,0</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>2,69; 45,49</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>4,97; 44,0</t>
         </is>
       </c>
     </row>
@@ -1227,27 +1091,17 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-1,23%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-1,23%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
           <t>-0,2%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 1,3</t>
+          <t>-3,5; 1,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 3,73</t>
+          <t>-2,0; 3,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 2,87</t>
+          <t>-3,56; 3,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,77; 1,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 1,42</t>
+          <t>-2,29; 4,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 4,34</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-3,98; 3,49</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-4,22; 3,76</t>
         </is>
       </c>
     </row>
@@ -1308,13 +1152,13 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
     <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A14:A15"/>

--- a/data/trans_bre/IP41-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP41-Clase-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 2,13</t>
+          <t>-9,91; 2,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 5,02</t>
+          <t>-7,22; 4,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 5,27</t>
+          <t>-10,37; 5,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 2,3</t>
+          <t>-10,39; 2,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 5,52</t>
+          <t>-7,39; 4,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 6,27</t>
+          <t>-11,32; 6,52</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 3,06</t>
+          <t>-8,28; 3,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 7,62</t>
+          <t>-7,27; 7,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 2,56</t>
+          <t>-14,49; 1,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 3,24</t>
+          <t>-8,6; 4,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 8,93</t>
+          <t>-8,12; 8,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 3,04</t>
+          <t>-15,94; 2,35</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 11,75</t>
+          <t>-0,9; 10,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 5,86</t>
+          <t>-6,16; 6,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 7,07</t>
+          <t>-7,46; 7,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 13,47</t>
+          <t>-0,93; 12,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 6,64</t>
+          <t>-6,45; 6,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 8,1</t>
+          <t>-7,8; 8,32</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 5,34</t>
+          <t>-4,26; 5,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 7,04</t>
+          <t>-3,99; 7,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 4,52</t>
+          <t>-7,39; 4,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 6,12</t>
+          <t>-4,64; 6,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 8,47</t>
+          <t>-4,55; 8,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 5,66</t>
+          <t>-8,58; 5,84</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,03; -0,02</t>
+          <t>-12,15; -0,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 5,81</t>
+          <t>-7,69; 6,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 10,08</t>
+          <t>-5,97; 9,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,59; -0,08</t>
+          <t>-12,78; -0,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 7,28</t>
+          <t>-8,94; 8,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 12,95</t>
+          <t>-7,25; 11,5</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 8,48</t>
+          <t>-7,48; 8,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 14,16</t>
+          <t>-6,24; 13,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,7; 26,75</t>
+          <t>2,63; 26,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 9,96</t>
+          <t>-8,0; 10,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 17,81</t>
+          <t>-7,0; 16,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,97; 44,0</t>
+          <t>3,38; 42,24</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 1,27</t>
+          <t>-3,5; 1,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 3,73</t>
+          <t>-2,37; 3,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 3,08</t>
+          <t>-3,3; 3,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 1,41</t>
+          <t>-3,75; 1,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 4,32</t>
+          <t>-2,63; 3,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 3,76</t>
+          <t>-3,89; 3,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP41-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP41-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-3,93</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,15</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,82</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-4,2%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,21%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-3,2%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-3.930708584407328</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.146048642431119</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-2.819642447526371</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>-0.0419692166431545</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.01211236666382155</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.03196090913667079</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-9,91; 2,31</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-7,22; 4,34</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-10,37; 5,59</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-10,39; 2,51</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-7,39; 4,77</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-11,32; 6,52</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-9.907602846699005</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-7.219650534450841</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-10.36539946237041</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>-0.1038792808701003</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.07389608666051931</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.1132174137885175</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.313594798737495</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4.343819733408638</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>5.5864475566776</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0.02513441873991753</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.04772968510249286</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.06516714063863178</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-2,24</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,64</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-5,71</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-2,36%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-6,51%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-8,28; 3,84</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-7,27; 7,46</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-14,49; 1,93</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-8,6; 4,13</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-8,12; 8,67</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-15,94; 2,35</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-2.24298700317207</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.6436073181600332</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-5.712787949208575</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.02360648489528776</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.007243791219502585</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.06505602347864246</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>5,01</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,08</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,15</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,49%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-8.277737222383893</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-7.273830826741142</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-14.48624586043095</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.08598492967137328</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.08124608463866248</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.159402983367731</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-0,9; 10,81</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-6,16; 6,1</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-7,46; 7,36</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-0,93; 12,51</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-6,45; 6,79</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-7,8; 8,32</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.842738462025148</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>7.464328121809515</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.9292404926858</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.0412979587429723</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.08669374121071702</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.02345107389053495</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,239 +767,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,56</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2,22</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,21</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-1,46%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>5.013967099754568</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.07618586208386624</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1483376607809506</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0.0548706849703866</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.0008154166570516114</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.001613122048535904</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-4,26; 5,31</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,99; 7,36</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-7,39; 4,67</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-4,64; 6,04</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-4,55; 8,73</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-8,58; 5,84</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-0.9040356824441665</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-6.157755512842455</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-7.459818402334116</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-0.009295462411531806</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.0645205252114608</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.07800342896997947</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>10.81419470601499</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>6.099078517997969</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>7.357863883120297</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0.1251189826681538</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.06788897446361111</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.08320193075381105</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-5,62</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,56</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,33</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-6,01%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,67%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-12,15; -0,01</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-7,69; 6,64</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-5,97; 9,03</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-12,78; -0,04</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-8,94; 8,35</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-7,25; 11,5</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>0.5644025268437658</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>2.218203490775861</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-1.211955924161534</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.006272170044017544</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.02570144615667238</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.01460069501740091</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>0,22</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>4,18</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>14,88</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>21,65%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-4.262959404084561</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-3.985138345179066</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-7.386903549414907</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.04638740346626687</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.04546677112738636</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.08577571474387914</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-7,48; 8,88</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-6,24; 13,36</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>2,63; 26,11</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-8,0; 10,55</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-7,0; 16,67</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>3,38; 42,24</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>5.309939994689487</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>7.359607618021916</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>4.669923356074786</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.06041887806519618</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.08731311716528771</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.05840935532918264</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1074,77 +931,243 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-1,13</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,91</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,17</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,23%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-0,2%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-5.61779617621363</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.5596904182626705</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.328809975645928</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-0.06005639377454701</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.00669758927995573</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.01630196822980662</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-3,5; 1,43</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-2,37; 3,38</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-3,3; 3,05</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-3,75; 1,58</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-2,63; 3,9</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-3,89; 3,64</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-12.15120318368878</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-7.685827760119333</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-5.973367268024408</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-0.1278418024497168</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.08937468456771501</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.07252711202911367</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>-0.01164862707018863</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>6.639776273222727</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>9.034781405822983</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>-0.0004260796294325739</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.08346290399953189</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.1150423303846732</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0.2188758953483472</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>4.184078305191763</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>14.88466141497694</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.002441422001627946</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.04931784390989372</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.2164830684086373</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-7.481635519177718</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-6.238675376162899</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>2.628689800079758</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.08002821005028685</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.06995228530571074</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>0.03382110727266169</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>8.879049769327871</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>13.36211765608147</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>26.10683962515096</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.1055486449947801</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.1666593008883414</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.4224113223209617</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-1.130676169945977</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.908819236274816</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.1676604392614522</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>-0.01229374320467151</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.01034348707979041</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.002000992026023064</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-3.501376466581955</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-2.371068984335867</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-3.301296059112902</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>-0.03748137647365677</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.02626832783068597</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.03886594540103955</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1.434920588400505</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3.38191993478384</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>3.054268282699778</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>0.01578187705207047</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.03896297133621384</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.03644651587793135</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1153,15 +1176,15 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
